--- a/Current TAPPs/TEM_TAPP_v48.xlsx
+++ b/Current TAPPs/TEM_TAPP_v48.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -617,7 +617,7 @@
           <t>Keyed By</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
@@ -935,7 +935,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="1" t="n"/>
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1104,7 +1104,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="1" t="n"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1273,7 +1273,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="1" t="n"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1442,7 +1442,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="1" t="n"/>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1611,7 +1611,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="1" t="n"/>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1780,7 +1780,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="1" t="n"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1949,7 +1949,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="1" t="n"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2118,7 +2118,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="1" t="n"/>
       <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2287,7 +2287,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Encourages formal procedure registration and ensures traceability.</t>
         </is>
@@ -2456,7 +2456,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session, which may cover several samples, and this is the link back to the raw instrument files.</t>
         </is>
@@ -2545,7 +2545,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="1" t="n"/>
       <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2714,7 +2714,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="1" t="n"/>
       <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2883,7 +2883,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="1" t="n"/>
       <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3052,7 +3052,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3221,7 +3221,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3390,7 +3390,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="1" t="n"/>
       <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3559,7 +3559,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>Provides a stable, citable link to the companion method independent of whether a dataset has been deposited.</t>
         </is>
@@ -3732,7 +3732,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="1" t="n"/>
       <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3865,7 +3865,7 @@
       <c r="G21" s="1" t="n"/>
       <c r="H21" s="1" t="n"/>
       <c r="I21" s="1" t="n"/>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="1" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
@@ -4111,7 +4111,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>Used for discoverability and procedure matching, and because the material type constrains sample preparation, calibration and matrix-matching requirements.</t>
         </is>
@@ -4284,7 +4284,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
+      <c r="J24" s="1" t="n"/>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4449,7 +4449,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
+      <c r="J25" s="1" t="n"/>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4618,7 +4618,7 @@
           <t>defines: sample</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session and may cover several samples.</t>
         </is>
@@ -4791,7 +4791,7 @@
           <t>defines: sampling unit</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="1" t="n"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4876,7 +4876,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="1" t="n"/>
       <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5041,7 +5041,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="1" t="n"/>
       <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5122,7 +5122,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
+      <c r="J30" s="1" t="n"/>
       <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5171,7 +5171,7 @@
       <c r="G31" s="1" t="n"/>
       <c r="H31" s="1" t="n"/>
       <c r="I31" s="1" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="1" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
@@ -5417,7 +5417,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>Recording it as a controlled value lets procedures be found by vendor.</t>
         </is>
@@ -5590,7 +5590,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="1" t="n"/>
       <c r="K34" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5755,7 +5755,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n"/>
+      <c r="J35" s="1" t="n"/>
       <c r="K35" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5920,7 +5920,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>Probe Cs-correction enables sub-Å STEM resolution and improved analytical signal; image Cs-correction reduces delocalization artifacts in HRTEM.</t>
         </is>
@@ -6089,7 +6089,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>Relevant for EELS energy resolution and EFTEM performance.</t>
         </is>
@@ -6258,7 +6258,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Cryo holders (liquid N2 to ~110 K) are critical for minimizing beam-induced damage to organic matter and beam-sensitive phases. Heating holders enable in-situ experiments.</t>
         </is>
@@ -6427,7 +6427,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n"/>
+      <c r="J39" s="1" t="n"/>
       <c r="K39" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6592,7 +6592,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="n"/>
+      <c r="J40" s="1" t="n"/>
       <c r="K40" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6757,7 +6757,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n"/>
+      <c r="J41" s="1" t="n"/>
       <c r="K41" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6922,7 +6922,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="1" t="n"/>
       <c r="K42" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7087,7 +7087,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="n"/>
+      <c r="J43" s="1" t="n"/>
       <c r="K43" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -7256,7 +7256,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
+      <c r="J44" s="1" t="n"/>
       <c r="K44" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7421,7 +7421,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="n"/>
+      <c r="J45" s="1" t="n"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -7590,7 +7590,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
+      <c r="J46" s="1" t="n"/>
       <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7723,7 +7723,7 @@
       <c r="G47" s="1" t="n"/>
       <c r="H47" s="1" t="n"/>
       <c r="I47" s="1" t="n"/>
-      <c r="J47" s="2" t="n"/>
+      <c r="J47" s="1" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
@@ -7969,7 +7969,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
         <is>
           <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability. Ensures every procedure record is self-describing and comparable across the library.</t>
         </is>
@@ -8054,7 +8054,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>For beam-sensitive materials (organic matter, phyllosilicates), 60–80 kV may be used to stay below the displacement threshold for C, N, O, and S. Key parameter for the beam damage regime.</t>
         </is>
@@ -8223,7 +8223,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="n"/>
+      <c r="J51" s="1" t="n"/>
       <c r="K51" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8388,7 +8388,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>In BF-TEM, a small aperture blocks diffracted beams to enhance mass-thickness contrast; in DF-TEM, the aperture is displaced to select a specific diffracted beam; in HRTEM, no aperture is typically used.</t>
         </is>
@@ -8557,7 +8557,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J53" s="2" t="n"/>
+      <c r="J53" s="1" t="n"/>
       <c r="K53" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8722,7 +8722,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>The inner angle determines the boundary between diffracted and thermally diffuse scattered electrons; larger inner angles yield stronger Z-contrast and reduced Bragg contrast. In HAADF-STEM a shorter camera length increases the inner angle, yielding more thermally diffuse (Z-contrast) and less Bragg-diffraction signal. The inner angle is the most critical.</t>
         </is>
@@ -8891,7 +8891,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
         <is>
           <t>Controls probe size (smaller angle = larger probe but less coherent), depth of field, and in 4D-STEM, the size of diffraction discs vs. spatial resolution. For near-parallel-beam 4D-STEM (e.g., phyllosilicate phase mapping), values as small as 0.1 mrad are used.</t>
         </is>
@@ -9060,7 +9060,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
         <is>
           <t>Serves as a direct spatial resolution proxy for STEM imaging and STEM-EDS/EELS analysis.</t>
         </is>
@@ -9229,7 +9229,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>Higher current improves EDS/EELS signal but increases beam damage risk, especially for organic matter and hydrous minerals.</t>
         </is>
@@ -9398,7 +9398,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>Longer dwell improves signal-to-noise but increases total specimen dose.</t>
         </is>
@@ -9567,7 +9567,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>Combined with calibrated pixel size, defines the field of view.</t>
         </is>
@@ -9736,7 +9736,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>Averaging reduces noise while limiting per-frame dose.</t>
         </is>
@@ -9905,7 +9905,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
         <is>
           <t>In STEM mode, also sets HAADF/ABF detector collection angles. Camera length choice affects HAADF Z-contrast purity: a shorter camera length (e.g. 30 mm) shifts the inner angle toward thermal diffuse scatter; a longer one (e.g. 150 mm) admits more Bragg scatter. Controls the mapping between reciprocal-space scattering angle and detector position.</t>
         </is>
@@ -10074,7 +10074,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J62" s="2" t="n"/>
+      <c r="J62" s="1" t="n"/>
       <c r="K62" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -10239,7 +10239,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>Hollow-cone illumination reduces dynamical diffraction effects and produces more kinematical-like intensities.</t>
         </is>
@@ -10408,7 +10408,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="n"/>
+      <c r="J64" s="1" t="n"/>
       <c r="K64" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -10573,7 +10573,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t>Longer dwell improves signal-to-noise for weakly diffracting phases (e.g., smectite 001 reflection at ~1.24 nm) but increases total specimen dose; risk of beam damage to phyllosilicates and organic matter must be balanced against data quality.</t>
         </is>
@@ -10742,7 +10742,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J66" s="2" t="n"/>
+      <c r="J66" s="1" t="n"/>
       <c r="K66" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -10907,7 +10907,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J67" s="2" t="n"/>
+      <c r="J67" s="1" t="n"/>
       <c r="K67" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11072,7 +11072,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J68" s="2" t="n"/>
+      <c r="J68" s="1" t="n"/>
       <c r="K68" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11237,7 +11237,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J69" s="2" t="n"/>
+      <c r="J69" s="1" t="n"/>
       <c r="K69" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11402,7 +11402,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J70" s="2" t="n"/>
+      <c r="J70" s="1" t="n"/>
       <c r="K70" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11571,7 +11571,7 @@
           <t>defines: analyte</t>
         </is>
       </c>
-      <c r="J71" s="2" t="n"/>
+      <c r="J71" s="1" t="n"/>
       <c r="K71" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11740,7 +11740,7 @@
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" s="1" t="inlineStr">
         <is>
           <t>A procedure may acquire many channels and report a small number of derived quantities; without this field a data consumer cannot tell which.</t>
         </is>
@@ -11825,7 +11825,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J73" s="2" t="n"/>
+      <c r="J73" s="1" t="n"/>
       <c r="K73" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11990,7 +11990,7 @@
           <t>defines: channel per analyte</t>
         </is>
       </c>
-      <c r="J74" s="2" t="n"/>
+      <c r="J74" s="1" t="n"/>
       <c r="K74" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12155,7 +12155,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J75" s="1" t="inlineStr">
         <is>
           <t>Controls the fraction of inelastically scattered electrons collected and the spectral background level.</t>
         </is>
@@ -12324,7 +12324,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="1" t="inlineStr">
         <is>
           <t>Controls the energy range acquired per readout and the effective energy resolution trade-off.</t>
         </is>
@@ -12493,7 +12493,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J77" s="1" t="inlineStr">
         <is>
           <t>Reflects combined electron source energy spread and monochromator effect (if active). Critical for ELNES fine-structure interpretation.</t>
         </is>
@@ -12662,7 +12662,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="1" t="n"/>
       <c r="K78" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12827,7 +12827,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J79" s="2" t="n"/>
+      <c r="J79" s="1" t="n"/>
       <c r="K79" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12960,7 +12960,7 @@
       <c r="G80" s="1" t="n"/>
       <c r="H80" s="1" t="n"/>
       <c r="I80" s="1" t="n"/>
-      <c r="J80" s="2" t="n"/>
+      <c r="J80" s="1" t="n"/>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
@@ -13202,7 +13202,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n"/>
+      <c r="J82" s="1" t="n"/>
       <c r="K82" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13367,7 +13367,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="1" t="n"/>
       <c r="K83" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -13532,7 +13532,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="1" t="n"/>
       <c r="K84" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13697,7 +13697,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J85" s="1" t="inlineStr">
         <is>
           <t>Critical for specimens thicker than ~0.5 inelastic mean free paths.</t>
         </is>
@@ -13866,7 +13866,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J86" s="1" t="inlineStr">
         <is>
           <t>The same edge yields different valence estimates under different calibrations and reference spectra, so a reported oxidation state is not comparable between studies unless the method and its reference data are stated.</t>
         </is>
@@ -14035,7 +14035,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n"/>
+      <c r="J87" s="1" t="n"/>
       <c r="K87" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14200,7 +14200,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n"/>
+      <c r="J88" s="1" t="n"/>
       <c r="K88" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14365,7 +14365,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t>Required for EELS quantification (log-ratio) and for assessing multiple-scattering severity.</t>
         </is>
@@ -14534,7 +14534,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n"/>
+      <c r="J90" s="1" t="n"/>
       <c r="K90" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14615,7 +14615,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>Criteria and outcome are combined in one field because neither is interpretable without the other, following the precision/accuracy precedent.</t>
         </is>
@@ -14704,7 +14704,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="1" t="n"/>
       <c r="K92" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14753,7 +14753,7 @@
       <c r="G93" s="1" t="n"/>
       <c r="H93" s="1" t="n"/>
       <c r="I93" s="1" t="n"/>
-      <c r="J93" s="2" t="n"/>
+      <c r="J93" s="1" t="n"/>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="n"/>
       <c r="M93" s="2" t="n"/>
@@ -14995,7 +14995,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>TEM-EDS is less standardized than EPMA; many procedures rely on manufacturer k-factors without external calibration.</t>
         </is>
@@ -15164,7 +15164,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J96" s="1" t="inlineStr">
         <is>
           <t>Accurate calibration is required for ELNES edge identification, chemical-state analysis, and inter-lab comparability.</t>
         </is>
@@ -15333,7 +15333,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n"/>
+      <c r="J97" s="1" t="n"/>
       <c r="K97" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -15498,7 +15498,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n"/>
+      <c r="J98" s="1" t="n"/>
       <c r="K98" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15663,7 +15663,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="n"/>
+      <c r="J99" s="1" t="n"/>
       <c r="K99" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -15828,7 +15828,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J100" s="1" t="inlineStr">
         <is>
           <t>Values above ~40% indicate excessive count rate and may degrade spectral quality and quantitative accuracy. EDS dead time correction is managed automatically by the detector electronics.</t>
         </is>
@@ -15997,7 +15997,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J101" s="2" t="n"/>
+      <c r="J101" s="1" t="n"/>
       <c r="K101" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16162,7 +16162,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>Answers whether a reported aggregate is defensible as a single population. The value cannot be known before the analysis.</t>
         </is>
@@ -16251,7 +16251,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n"/>
+      <c r="J103" s="1" t="n"/>
       <c r="K103" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16385,7 +16385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16509,7 +16509,7 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>TEM Imaging</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
@@ -16517,7 +16517,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>TEM Imaging</t>
+          <t>STEM Imaging</t>
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
@@ -16525,250 +16525,242 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>STEM Imaging</t>
+          <t>Electron Diffraction</t>
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Electron Diffraction</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n"/>
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>This field applies to this analytical mode and should be reported.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>This field applies to this analytical mode and should be reported.</t>
+          <t>This field does not apply to this analytical mode.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>This field does not apply to this analytical mode.</t>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>What to enter</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>What to enter</t>
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>Controlled list</t>
+          <t>Controlled list / Text</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>Controlled list / Text</t>
+          <t>Numeric (unit)</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Numeric (unit)</t>
+          <t>Numeric + unit</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
+          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Numeric + unit</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
+          <t>Free text. No controlled vocabulary applies.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>N/A | None</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Free text. No controlled vocabulary applies.</t>
+          <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>N/A | None</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Keyed By (Rule 7)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>What the field's value repeats over</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Keyed By (Rule 7)</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>What the field's value repeats over</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Scalar — one value per procedure or analysis. The default.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Scalar — one value per procedure or analysis. The default.</t>
+          <t>One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>defines: analyte</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>defines: analyte</t>
+          <t>defines: channel per analyte</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per analyte. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>defines: channel per analyte</t>
+          <t>defines: reported property</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per analyte. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>defines: reported property</t>
+          <t>defines: sample</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
+          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>defines: sample</t>
+          <t>defines: sampling unit</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>defines: sampling unit</t>
+          <t>reported property</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
+          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>reported property</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
-        </is>
-      </c>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>Nested — sampling unit exists only within sample. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
